--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +473,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="B2" t="n">
@@ -504,14 +504,18 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="B3" t="n">
@@ -542,14 +546,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="B4" t="n">
@@ -580,14 +588,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="B5" t="n">
@@ -618,14 +624,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B6" t="n">
@@ -656,14 +660,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B7" t="n">
@@ -694,14 +696,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B8" t="n">
@@ -732,14 +732,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B9" t="n">
@@ -770,14 +768,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B10" t="n">
@@ -808,14 +804,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B11" t="n">
@@ -846,14 +840,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B12" t="n">
@@ -884,14 +876,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B13" t="n">
@@ -922,14 +912,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B14" t="n">
@@ -960,14 +948,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B15" t="n">
@@ -998,14 +984,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B16" t="n">
@@ -1036,14 +1020,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B17" t="n">
@@ -1074,14 +1056,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B18" t="n">
@@ -1112,14 +1092,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B19" t="n">
@@ -1150,14 +1128,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B20" t="n">
@@ -1188,14 +1164,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B21" t="n">
@@ -1226,14 +1200,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B22" t="n">
@@ -1264,14 +1236,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B23" t="n">
@@ -1302,14 +1272,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B24" t="n">
@@ -1340,14 +1308,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B25" t="n">
@@ -1378,14 +1344,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B26" t="n">
@@ -1416,14 +1380,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B27" t="n">
@@ -1454,14 +1416,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B28" t="n">
@@ -1492,14 +1452,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B29" t="n">
@@ -1530,14 +1488,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B30" t="n">
@@ -1568,14 +1524,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B31" t="n">
@@ -1606,14 +1560,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46279</v>
       </c>
       <c r="B32" t="n">
@@ -1644,14 +1596,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46279</v>
       </c>
       <c r="B33" t="n">
@@ -1682,14 +1632,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="B34" t="n">
@@ -1720,14 +1668,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="B35" t="n">
@@ -1758,14 +1704,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B36" t="n">
@@ -1796,14 +1740,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B37" t="n">
@@ -1834,14 +1776,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B38" t="n">
@@ -1872,14 +1812,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B39" t="n">
@@ -1910,14 +1848,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B40" t="n">
@@ -1948,14 +1884,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B41" t="n">
@@ -1986,14 +1920,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B42" t="n">
@@ -2024,14 +1956,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B43" t="n">
@@ -2062,14 +1992,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B44" t="n">
@@ -2100,14 +2028,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B45" t="n">
@@ -2138,14 +2064,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B46" t="n">
@@ -2176,14 +2100,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B47" t="n">
@@ -2214,14 +2136,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B48" t="n">
@@ -2252,14 +2172,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B49" t="n">
@@ -2290,14 +2208,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B50" t="n">
@@ -2328,14 +2244,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B51" t="n">
@@ -2366,14 +2280,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B52" t="n">
@@ -2404,14 +2316,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B53" t="n">
@@ -2442,14 +2352,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B54" t="n">
@@ -2480,14 +2388,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B55" t="n">
@@ -2518,14 +2424,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B56" t="n">
@@ -2556,14 +2460,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B57" t="n">
@@ -2594,14 +2496,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B58" t="n">
@@ -2632,14 +2532,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B59" t="n">
@@ -2670,14 +2568,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B60" t="n">
@@ -2708,14 +2604,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B61" t="n">
@@ -2746,14 +2640,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B62" t="n">
@@ -2784,14 +2676,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B63" t="n">
@@ -2822,14 +2712,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46286</v>
       </c>
       <c r="B64" t="n">
@@ -2860,14 +2748,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46286</v>
       </c>
       <c r="B65" t="n">
@@ -2898,14 +2784,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46289</v>
       </c>
       <c r="B66" t="n">
@@ -2936,14 +2820,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46289</v>
       </c>
       <c r="B67" t="n">
@@ -2974,14 +2856,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B68" t="n">
@@ -3012,14 +2892,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B69" t="n">
@@ -3050,14 +2928,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B70" t="n">
@@ -3088,14 +2964,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B71" t="n">
@@ -3126,14 +3000,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B72" t="n">
@@ -3164,14 +3036,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B73" t="n">
@@ -3202,14 +3072,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B74" t="n">
@@ -3240,14 +3108,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B75" t="n">
@@ -3278,14 +3144,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B76" t="n">
@@ -3316,14 +3180,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B77" t="n">
@@ -3354,14 +3216,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B78" t="n">
@@ -3392,14 +3252,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B79" t="n">
@@ -3430,14 +3288,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B80" t="n">
@@ -3468,14 +3324,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B81" t="n">
@@ -3506,14 +3360,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B82" t="n">
@@ -3544,14 +3396,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B83" t="n">
@@ -3582,14 +3432,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B84" t="n">
@@ -3620,14 +3468,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B85" t="n">
@@ -3658,14 +3504,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B86" t="n">
@@ -3696,14 +3540,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B87" t="n">
@@ -3734,14 +3576,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B88" t="n">
@@ -3772,14 +3612,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B89" t="n">
@@ -3810,14 +3648,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B90" t="n">
@@ -3848,14 +3684,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B91" t="n">
@@ -3886,14 +3720,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B92" t="n">
@@ -3924,14 +3756,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B93" t="n">
@@ -3962,14 +3792,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B94" t="n">
@@ -4000,14 +3828,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B95" t="n">
@@ -4038,14 +3864,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46293</v>
       </c>
       <c r="B96" t="n">
@@ -4076,14 +3900,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46293</v>
       </c>
       <c r="B97" t="n">
@@ -4114,14 +3936,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46296</v>
       </c>
       <c r="B98" t="n">
@@ -4152,14 +3972,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46296</v>
       </c>
       <c r="B99" t="n">
@@ -4190,14 +4008,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B100" t="n">
@@ -4228,14 +4044,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B101" t="n">
@@ -4266,14 +4080,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B102" t="n">
@@ -4304,14 +4116,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B103" t="n">
@@ -4342,14 +4152,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B104" t="n">
@@ -4380,14 +4188,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B105" t="n">
@@ -4418,14 +4224,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B106" t="n">
@@ -4456,14 +4260,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B107" t="n">
@@ -4494,14 +4296,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B108" t="n">
@@ -4532,14 +4332,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B109" t="n">
@@ -4570,14 +4368,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B110" t="n">
@@ -4608,14 +4404,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B111" t="n">
@@ -4646,14 +4440,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B112" t="n">
@@ -4684,14 +4476,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B113" t="n">
@@ -4722,14 +4512,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B114" t="n">
@@ -4760,14 +4548,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B115" t="n">
@@ -4798,14 +4584,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B116" t="n">
@@ -4836,14 +4620,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B117" t="n">
@@ -4874,14 +4656,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B118" t="n">
@@ -4912,14 +4692,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B119" t="n">
@@ -4950,14 +4728,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B120" t="n">
@@ -4988,14 +4764,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B121" t="n">
@@ -5026,14 +4800,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B122" t="n">
@@ -5064,14 +4836,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B123" t="n">
@@ -5102,14 +4872,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B124" t="n">
@@ -5140,14 +4908,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B125" t="n">
@@ -5178,14 +4944,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B126" t="n">
@@ -5216,14 +4980,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46299</v>
       </c>
       <c r="B127" t="n">
@@ -5254,14 +5016,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46300</v>
       </c>
       <c r="B128" t="n">
@@ -5292,14 +5052,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46300</v>
       </c>
       <c r="B129" t="n">
@@ -5330,14 +5088,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46303</v>
       </c>
       <c r="B130" t="n">
@@ -5368,14 +5124,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46303</v>
       </c>
       <c r="B131" t="n">
@@ -5406,14 +5160,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B132" t="n">
@@ -5444,14 +5196,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B133" t="n">
@@ -5482,14 +5232,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B134" t="n">
@@ -5520,14 +5268,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B135" t="n">
@@ -5558,14 +5304,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B136" t="n">
@@ -5596,14 +5340,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B137" t="n">
@@ -5634,14 +5376,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B138" t="n">
@@ -5672,14 +5412,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B139" t="n">
@@ -5710,14 +5448,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B140" t="n">
@@ -5748,14 +5484,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B141" t="n">
@@ -5786,14 +5520,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B142" t="n">
@@ -5824,14 +5556,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B143" t="n">
@@ -5862,14 +5592,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B144" t="n">
@@ -5900,14 +5628,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B145" t="n">
@@ -5938,14 +5664,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B146" t="n">
@@ -5976,14 +5700,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B147" t="n">
@@ -6014,14 +5736,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B148" t="n">
@@ -6052,14 +5772,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B149" t="n">
@@ -6090,14 +5808,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B150" t="n">
@@ -6128,14 +5844,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B151" t="n">
@@ -6166,14 +5880,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B152" t="n">
@@ -6204,14 +5916,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B153" t="n">
@@ -6242,14 +5952,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B154" t="n">
@@ -6280,14 +5988,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B155" t="n">
@@ -6318,14 +6024,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B156" t="n">
@@ -6356,14 +6060,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46306</v>
       </c>
       <c r="B157" t="n">
@@ -6394,14 +6096,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46307</v>
       </c>
       <c r="B158" t="n">
@@ -6432,14 +6132,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46307</v>
       </c>
       <c r="B159" t="n">
@@ -6470,14 +6168,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46310</v>
       </c>
       <c r="B160" t="n">
@@ -6508,14 +6204,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46310</v>
       </c>
       <c r="B161" t="n">
@@ -6546,14 +6240,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B162" t="n">
@@ -6584,14 +6276,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B163" t="n">
@@ -6622,14 +6312,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B164" t="n">
@@ -6660,14 +6348,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B165" t="n">
@@ -6698,14 +6384,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B166" t="n">
@@ -6736,14 +6420,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B167" t="n">
@@ -6774,14 +6456,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B168" t="n">
@@ -6812,14 +6492,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B169" t="n">
@@ -6850,14 +6528,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B170" t="n">
@@ -6888,14 +6564,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B171" t="n">
@@ -6926,14 +6600,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B172" t="n">
@@ -6964,14 +6636,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B173" t="n">
@@ -7002,14 +6672,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B174" t="n">
@@ -7040,14 +6708,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B175" t="n">
@@ -7078,14 +6744,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B176" t="n">
@@ -7116,14 +6780,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B177" t="n">
@@ -7154,14 +6816,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B178" t="n">
@@ -7192,14 +6852,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B179" t="n">
@@ -7230,14 +6888,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B180" t="n">
@@ -7268,14 +6924,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B181" t="n">
@@ -7306,14 +6960,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B182" t="n">
@@ -7344,14 +6996,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B183" t="n">
@@ -7382,14 +7032,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B184" t="n">
@@ -7420,14 +7068,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46313</v>
       </c>
       <c r="B185" t="n">
@@ -7458,14 +7104,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46314</v>
       </c>
       <c r="B186" t="n">
@@ -7496,14 +7140,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46314</v>
       </c>
       <c r="B187" t="n">
@@ -7534,14 +7176,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46317</v>
       </c>
       <c r="B188" t="n">
@@ -7572,14 +7212,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46317</v>
       </c>
       <c r="B189" t="n">
@@ -7610,14 +7248,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B190" t="n">
@@ -7648,14 +7284,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B191" t="n">
@@ -7686,14 +7320,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B192" t="n">
@@ -7724,14 +7356,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B193" t="n">
@@ -7762,14 +7392,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B194" t="n">
@@ -7800,14 +7428,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B195" t="n">
@@ -7838,14 +7464,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B196" t="n">
@@ -7876,14 +7500,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B197" t="n">
@@ -7914,14 +7536,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B198" t="n">
@@ -7952,14 +7572,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B199" t="n">
@@ -7990,14 +7608,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B200" t="n">
@@ -8028,14 +7644,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B201" t="n">
@@ -8066,14 +7680,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B202" t="n">
@@ -8104,14 +7716,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B203" t="n">
@@ -8142,14 +7752,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B204" t="n">
@@ -8180,14 +7788,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B205" t="n">
@@ -8218,14 +7824,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B206" t="n">
@@ -8256,14 +7860,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B207" t="n">
@@ -8294,14 +7896,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B208" t="n">
@@ -8332,14 +7932,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B209" t="n">
@@ -8370,14 +7968,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B210" t="n">
@@ -8408,14 +8004,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B211" t="n">
@@ -8446,14 +8040,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B212" t="n">
@@ -8484,14 +8076,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>46320</v>
       </c>
       <c r="B213" t="n">
@@ -8522,14 +8112,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>46321</v>
       </c>
       <c r="B214" t="n">
@@ -8560,14 +8148,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46321</v>
       </c>
       <c r="B215" t="n">
@@ -8598,14 +8184,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46324</v>
       </c>
       <c r="B216" t="n">
@@ -8636,14 +8220,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46324</v>
       </c>
       <c r="B217" t="n">
@@ -8674,14 +8256,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B218" t="n">
@@ -8712,14 +8292,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B219" t="n">
@@ -8750,14 +8328,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B220" t="n">
@@ -8788,14 +8364,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B221" t="n">
@@ -8826,14 +8400,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B222" t="n">
@@ -8864,14 +8436,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B223" t="n">
@@ -8902,14 +8472,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B224" t="n">
@@ -8940,14 +8508,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B225" t="n">
@@ -8978,14 +8544,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B226" t="n">
@@ -9016,14 +8580,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B227" t="n">
@@ -9054,14 +8616,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B228" t="n">
@@ -9092,14 +8652,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B229" t="n">
@@ -9130,14 +8688,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B230" t="n">
@@ -9168,14 +8724,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B231" t="n">
@@ -9206,14 +8760,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B232" t="n">
@@ -9244,14 +8796,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B233" t="n">
@@ -9282,14 +8832,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B234" t="n">
@@ -9320,14 +8868,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B235" t="n">
@@ -9358,14 +8904,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B236" t="n">
@@ -9396,14 +8940,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B237" t="n">
@@ -9434,14 +8976,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B238" t="n">
@@ -9472,14 +9012,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B239" t="n">
@@ -9510,14 +9048,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B240" t="n">
@@ -9548,14 +9084,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46327</v>
       </c>
       <c r="B241" t="n">
@@ -9586,14 +9120,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46328</v>
       </c>
       <c r="B242" t="n">
@@ -9624,14 +9156,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46328</v>
       </c>
       <c r="B243" t="n">
@@ -9662,14 +9192,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46331</v>
       </c>
       <c r="B244" t="n">
@@ -9700,14 +9228,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46331</v>
       </c>
       <c r="B245" t="n">
@@ -9738,14 +9264,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B246" t="n">
@@ -9776,14 +9300,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B247" t="n">
@@ -9814,14 +9336,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B248" t="n">
@@ -9852,14 +9372,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B249" t="n">
@@ -9890,14 +9408,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B250" t="n">
@@ -9928,14 +9444,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B251" t="n">
@@ -9966,14 +9480,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B252" t="n">
@@ -10004,14 +9516,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B253" t="n">
@@ -10042,14 +9552,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B254" t="n">
@@ -10080,14 +9588,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B255" t="n">
@@ -10118,14 +9624,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B256" t="n">
@@ -10156,14 +9660,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B257" t="n">
@@ -10194,14 +9696,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B258" t="n">
@@ -10232,14 +9732,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B259" t="n">
@@ -10270,14 +9768,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B260" t="n">
@@ -10308,14 +9804,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B261" t="n">
@@ -10346,14 +9840,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B262" t="n">
@@ -10384,14 +9876,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B263" t="n">
@@ -10422,14 +9912,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B264" t="n">
@@ -10460,14 +9948,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B265" t="n">
@@ -10498,14 +9984,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B266" t="n">
@@ -10536,14 +10020,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B267" t="n">
@@ -10574,14 +10056,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B268" t="n">
@@ -10612,14 +10092,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B269" t="n">
@@ -10650,14 +10128,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B270" t="n">
@@ -10688,14 +10164,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="B271" t="n">
@@ -10726,14 +10200,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>46335</v>
       </c>
       <c r="B272" t="n">
@@ -10764,14 +10236,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>46335</v>
       </c>
       <c r="B273" t="n">
@@ -10802,14 +10272,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>46338</v>
       </c>
       <c r="B274" t="n">
@@ -10840,14 +10308,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>46338</v>
       </c>
       <c r="B275" t="n">
@@ -10878,14 +10344,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B276" t="n">
@@ -10916,14 +10380,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B277" t="n">
@@ -10954,14 +10416,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B278" t="n">
@@ -10992,14 +10452,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B279" t="n">
@@ -11030,14 +10488,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B280" t="n">
@@ -11068,14 +10524,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B281" t="n">
@@ -11106,14 +10560,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B282" t="n">
@@ -11144,14 +10596,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B283" t="n">
@@ -11182,14 +10632,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B284" t="n">
@@ -11220,14 +10668,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
       <c r="J284" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B285" t="n">
@@ -11258,14 +10704,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B286" t="n">
@@ -11296,14 +10740,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B287" t="n">
@@ -11334,14 +10776,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B288" t="n">
@@ -11372,14 +10812,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B289" t="n">
@@ -11410,14 +10848,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B290" t="n">
@@ -11448,14 +10884,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B291" t="n">
@@ -11486,14 +10920,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B292" t="n">
@@ -11524,14 +10956,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B293" t="n">
@@ -11562,14 +10992,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B294" t="n">
@@ -11600,14 +11028,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B295" t="n">
@@ -11638,14 +11064,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B296" t="n">
@@ -11676,14 +11100,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B297" t="n">
@@ -11714,14 +11136,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B298" t="n">
@@ -11752,14 +11172,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="B299" t="n">
@@ -11790,14 +11208,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46342</v>
       </c>
       <c r="B300" t="n">
@@ -11828,14 +11244,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46342</v>
       </c>
       <c r="B301" t="n">
@@ -11866,14 +11280,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46345</v>
       </c>
       <c r="B302" t="n">
@@ -11904,14 +11316,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46345</v>
       </c>
       <c r="B303" t="n">
@@ -11942,14 +11352,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B304" t="n">
@@ -11980,14 +11388,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B305" t="n">
@@ -12018,14 +11424,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B306" t="n">
@@ -12056,14 +11460,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
       <c r="J306" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B307" t="n">
@@ -12094,14 +11496,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B308" t="n">
@@ -12132,14 +11532,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B309" t="n">
@@ -12170,14 +11568,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B310" t="n">
@@ -12208,14 +11604,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
       <c r="J310" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B311" t="n">
@@ -12246,14 +11640,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B312" t="n">
@@ -12284,14 +11676,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B313" t="n">
@@ -12322,14 +11712,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B314" t="n">
@@ -12360,14 +11748,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B315" t="n">
@@ -12398,14 +11784,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B316" t="n">
@@ -12436,14 +11820,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B317" t="n">
@@ -12474,14 +11856,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B318" t="n">
@@ -12512,14 +11892,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B319" t="n">
@@ -12550,14 +11928,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B320" t="n">
@@ -12588,14 +11964,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B321" t="n">
@@ -12626,14 +12000,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B322" t="n">
@@ -12664,14 +12036,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B323" t="n">
@@ -12702,14 +12072,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B324" t="n">
@@ -12740,14 +12108,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>46348</v>
       </c>
       <c r="B325" t="n">
@@ -12778,14 +12144,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>46349</v>
       </c>
       <c r="B326" t="n">
@@ -12816,14 +12180,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>46349</v>
       </c>
       <c r="B327" t="n">
@@ -12854,14 +12216,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>46351</v>
       </c>
       <c r="B328" t="n">
@@ -12892,14 +12252,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>46351</v>
       </c>
       <c r="B329" t="n">
@@ -12930,14 +12288,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B330" t="n">
@@ -12968,14 +12324,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B331" t="n">
@@ -13006,14 +12360,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B332" t="n">
@@ -13044,14 +12396,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
       <c r="J332" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B333" t="n">
@@ -13082,14 +12432,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
       <c r="J333" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B334" t="n">
@@ -13120,14 +12468,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
       <c r="J334" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>46352</v>
       </c>
       <c r="B335" t="n">
@@ -13158,14 +12504,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
       <c r="J335" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>46353</v>
       </c>
       <c r="B336" t="n">
@@ -13196,14 +12540,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
       <c r="J336" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>46353</v>
       </c>
       <c r="B337" t="n">
@@ -13234,14 +12576,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
       <c r="J337" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B338" t="n">
@@ -13272,14 +12612,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr"/>
       <c r="J338" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B339" t="n">
@@ -13310,14 +12648,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
       <c r="J339" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B340" t="n">
@@ -13348,14 +12684,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
       <c r="J340" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B341" t="n">
@@ -13386,14 +12720,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
       <c r="J341" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B342" t="n">
@@ -13424,14 +12756,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
       <c r="J342" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B343" t="n">
@@ -13462,14 +12792,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
       <c r="J343" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B344" t="n">
@@ -13500,14 +12828,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
       <c r="J344" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B345" t="n">
@@ -13538,14 +12864,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
       <c r="J345" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B346" t="n">
@@ -13576,14 +12900,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr"/>
       <c r="J346" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B347" t="n">
@@ -13614,14 +12936,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
       <c r="J347" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B348" t="n">
@@ -13652,14 +12972,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
       <c r="J348" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B349" t="n">
@@ -13690,14 +13008,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
       <c r="J349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B350" t="n">
@@ -13728,14 +13044,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
       <c r="J350" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B351" t="n">
@@ -13766,14 +13080,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
       <c r="J351" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B352" t="n">
@@ -13804,14 +13116,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
       <c r="J352" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B353" t="n">
@@ -13842,14 +13152,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
       <c r="J353" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B354" t="n">
@@ -13880,14 +13188,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr"/>
       <c r="J354" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B355" t="n">
@@ -13918,14 +13224,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
       <c r="J355" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B356" t="n">
@@ -13956,14 +13260,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
       <c r="J356" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>46355</v>
       </c>
       <c r="B357" t="n">
@@ -13994,14 +13296,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="B358" t="n">
@@ -14032,14 +13332,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
       <c r="J358" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="B359" t="n">
@@ -14070,14 +13368,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
       <c r="J359" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>46359</v>
       </c>
       <c r="B360" t="n">
@@ -14108,14 +13404,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
       <c r="J360" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>46359</v>
       </c>
       <c r="B361" t="n">
@@ -14146,14 +13440,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
       <c r="J361" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B362" t="n">
@@ -14184,14 +13476,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
       <c r="J362" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B363" t="n">
@@ -14222,14 +13512,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
       <c r="J363" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B364" t="n">
@@ -14260,14 +13548,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
       <c r="J364" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B365" t="n">
@@ -14298,14 +13584,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
       <c r="J365" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B366" t="n">
@@ -14336,14 +13620,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
       <c r="J366" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B367" t="n">
@@ -14374,14 +13656,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
       <c r="J367" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B368" t="n">
@@ -14412,14 +13692,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
       <c r="J368" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B369" t="n">
@@ -14450,14 +13728,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
       <c r="J369" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B370" t="n">
@@ -14488,14 +13764,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
       <c r="J370" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B371" t="n">
@@ -14526,14 +13800,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
       <c r="J371" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B372" t="n">
@@ -14564,14 +13836,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
       <c r="J372" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B373" t="n">
@@ -14602,14 +13872,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr"/>
-      <c r="I373" t="inlineStr"/>
       <c r="J373" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B374" t="n">
@@ -14640,14 +13908,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
       <c r="J374" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B375" t="n">
@@ -14678,14 +13944,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr"/>
       <c r="J375" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B376" t="n">
@@ -14716,14 +13980,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
       <c r="J376" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B377" t="n">
@@ -14754,14 +14016,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
       <c r="J377" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B378" t="n">
@@ -14792,14 +14052,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr"/>
       <c r="J378" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B379" t="n">
@@ -14830,14 +14088,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
       <c r="J379" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B380" t="n">
@@ -14868,14 +14124,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
       <c r="J380" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B381" t="n">
@@ -14906,14 +14160,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B382" t="n">
@@ -14944,14 +14196,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
       <c r="J382" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B383" t="n">
@@ -14982,14 +14232,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
       <c r="J383" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B384" t="n">
@@ -15020,14 +14268,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
       <c r="J384" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="B385" t="n">
@@ -15058,14 +14304,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
       <c r="J385" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>46363</v>
       </c>
       <c r="B386" t="n">
@@ -15096,14 +14340,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
       <c r="J386" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>46363</v>
       </c>
       <c r="B387" t="n">
@@ -15134,14 +14376,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
       <c r="J387" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>46366</v>
       </c>
       <c r="B388" t="n">
@@ -15172,14 +14412,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
       <c r="J388" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>46366</v>
       </c>
       <c r="B389" t="n">
@@ -15210,14 +14448,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
       <c r="J389" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B390" t="n">
@@ -15248,14 +14484,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
       <c r="J390" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B391" t="n">
@@ -15286,14 +14520,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
       <c r="J391" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B392" t="n">
@@ -15324,14 +14556,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr"/>
-      <c r="I392" t="inlineStr"/>
       <c r="J392" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B393" t="n">
@@ -15362,14 +14592,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
       <c r="J393" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B394" t="n">
@@ -15400,14 +14628,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
       <c r="J394" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B395" t="n">
@@ -15438,14 +14664,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
       <c r="J395" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B396" t="n">
@@ -15476,14 +14700,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
-      <c r="I396" t="inlineStr"/>
       <c r="J396" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B397" t="n">
@@ -15514,14 +14736,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
       <c r="J397" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B398" t="n">
@@ -15552,14 +14772,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
       <c r="J398" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B399" t="n">
@@ -15590,14 +14808,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
       <c r="J399" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B400" t="n">
@@ -15628,14 +14844,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
       <c r="J400" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B401" t="n">
@@ -15666,14 +14880,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
       <c r="J401" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B402" t="n">
@@ -15704,14 +14916,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
       <c r="J402" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B403" t="n">
@@ -15742,14 +14952,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
       <c r="J403" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B404" t="n">
@@ -15780,14 +14988,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
       <c r="J404" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B405" t="n">
@@ -15818,14 +15024,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
       <c r="J405" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B406" t="n">
@@ -15856,14 +15060,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
       <c r="J406" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B407" t="n">
@@ -15894,14 +15096,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
       <c r="J407" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B408" t="n">
@@ -15932,14 +15132,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr"/>
       <c r="J408" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B409" t="n">
@@ -15970,14 +15168,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr"/>
-      <c r="I409" t="inlineStr"/>
       <c r="J409" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B410" t="n">
@@ -16008,14 +15204,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
       <c r="J410" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B411" t="n">
@@ -16046,14 +15240,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
       <c r="J411" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B412" t="n">
@@ -16084,14 +15276,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
-      <c r="I412" t="inlineStr"/>
       <c r="J412" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B413" t="n">
@@ -16122,14 +15312,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
       <c r="J413" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B414" t="n">
@@ -16160,14 +15348,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
       <c r="J414" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>46369</v>
       </c>
       <c r="B415" t="n">
@@ -16198,14 +15384,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
       <c r="J415" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>46370</v>
       </c>
       <c r="B416" t="n">
@@ -16236,14 +15420,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr"/>
       <c r="J416" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>46370</v>
       </c>
       <c r="B417" t="n">
@@ -16274,14 +15456,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
       <c r="J417" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>46373</v>
       </c>
       <c r="B418" t="n">
@@ -16312,14 +15492,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
       <c r="J418" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>46373</v>
       </c>
       <c r="B419" t="n">
@@ -16350,14 +15528,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
       <c r="J419" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>46375</v>
       </c>
       <c r="B420" t="n">
@@ -16388,14 +15564,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
       <c r="J420" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>46375</v>
       </c>
       <c r="B421" t="n">
@@ -16426,14 +15600,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>46375</v>
       </c>
       <c r="B422" t="n">
@@ -16464,14 +15636,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr"/>
-      <c r="I422" t="inlineStr"/>
       <c r="J422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>46375</v>
       </c>
       <c r="B423" t="n">
@@ -16502,14 +15672,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
       <c r="J423" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B424" t="n">
@@ -16540,14 +15708,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr"/>
       <c r="J424" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B425" t="n">
@@ -16578,14 +15744,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
       <c r="J425" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B426" t="n">
@@ -16616,14 +15780,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
       <c r="J426" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B427" t="n">
@@ -16654,14 +15816,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
       <c r="J427" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B428" t="n">
@@ -16692,14 +15852,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
       <c r="J428" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B429" t="n">
@@ -16730,14 +15888,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B430" t="n">
@@ -16768,14 +15924,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr"/>
-      <c r="I430" t="inlineStr"/>
       <c r="J430" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B431" t="n">
@@ -16806,14 +15960,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
       <c r="J431" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B432" t="n">
@@ -16844,14 +15996,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr"/>
-      <c r="I432" t="inlineStr"/>
       <c r="J432" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B433" t="n">
@@ -16882,14 +16032,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
       <c r="J433" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B434" t="n">
@@ -16920,14 +16068,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
       <c r="J434" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B435" t="n">
@@ -16958,14 +16104,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr"/>
       <c r="J435" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B436" t="n">
@@ -16996,14 +16140,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
       <c r="J436" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B437" t="n">
@@ -17034,14 +16176,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
       <c r="J437" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B438" t="n">
@@ -17072,14 +16212,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
       <c r="J438" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B439" t="n">
@@ -17110,14 +16248,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
       <c r="J439" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B440" t="n">
@@ -17148,14 +16284,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
       <c r="J440" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B441" t="n">
@@ -17186,14 +16320,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
       <c r="J441" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B442" t="n">
@@ -17224,14 +16356,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
       <c r="J442" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B443" t="n">
@@ -17262,14 +16392,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
       <c r="J443" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B444" t="n">
@@ -17300,14 +16428,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr"/>
       <c r="J444" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B445" t="n">
@@ -17338,14 +16464,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
       <c r="J445" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B446" t="n">
@@ -17376,14 +16500,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr"/>
       <c r="J446" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>46376</v>
       </c>
       <c r="B447" t="n">
@@ -17414,14 +16536,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
       <c r="J447" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>46377</v>
       </c>
       <c r="B448" t="n">
@@ -17452,14 +16572,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
       <c r="J448" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>46377</v>
       </c>
       <c r="B449" t="n">
@@ -17490,14 +16608,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
       <c r="J449" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>46380</v>
       </c>
       <c r="B450" t="n">
@@ -17528,14 +16644,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
       <c r="J450" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>46380</v>
       </c>
       <c r="B451" t="n">
@@ -17566,14 +16680,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
       <c r="J451" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B452" t="n">
@@ -17604,14 +16716,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
       <c r="J452" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B453" t="n">
@@ -17642,14 +16752,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
       <c r="J453" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B454" t="n">
@@ -17680,14 +16788,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
       <c r="J454" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B455" t="n">
@@ -17718,14 +16824,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
       <c r="J455" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B456" t="n">
@@ -17756,14 +16860,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
       <c r="J456" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>46381</v>
       </c>
       <c r="B457" t="n">
@@ -17794,14 +16896,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
       <c r="J457" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B458" t="n">
@@ -17832,14 +16932,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr"/>
       <c r="J458" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B459" t="n">
@@ -17870,14 +16968,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
       <c r="J459" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B460" t="n">
@@ -17908,14 +17004,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
       <c r="J460" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B461" t="n">
@@ -17946,14 +17040,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
       <c r="J461" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B462" t="n">
@@ -17984,14 +17076,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
       <c r="J462" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B463" t="n">
@@ -18022,14 +17112,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
       <c r="J463" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B464" t="n">
@@ -18060,14 +17148,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
       <c r="J464" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B465" t="n">
@@ -18098,14 +17184,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
       <c r="J465" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B466" t="n">
@@ -18136,14 +17220,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
       <c r="J466" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B467" t="n">
@@ -18174,14 +17256,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr"/>
-      <c r="I467" t="inlineStr"/>
       <c r="J467" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B468" t="n">
@@ -18212,14 +17292,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr"/>
       <c r="J468" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B469" t="n">
@@ -18250,14 +17328,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
       <c r="J469" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B470" t="n">
@@ -18288,14 +17364,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr"/>
       <c r="J470" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B471" t="n">
@@ -18326,14 +17400,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
       <c r="J471" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B472" t="n">
@@ -18364,14 +17436,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr"/>
       <c r="J472" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B473" t="n">
@@ -18402,14 +17472,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
       <c r="J473" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B474" t="n">
@@ -18440,14 +17508,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
-      <c r="I474" t="inlineStr"/>
       <c r="J474" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B475" t="n">
@@ -18478,14 +17544,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr"/>
       <c r="J475" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B476" t="n">
@@ -18516,14 +17580,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr"/>
-      <c r="I476" t="inlineStr"/>
       <c r="J476" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B477" t="n">
@@ -18554,14 +17616,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
       <c r="J477" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B478" t="n">
@@ -18592,14 +17652,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
       <c r="J478" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="B479" t="n">
@@ -18630,14 +17688,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
       <c r="J479" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>46384</v>
       </c>
       <c r="B480" t="n">
@@ -18668,14 +17724,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr"/>
-      <c r="I480" t="inlineStr"/>
       <c r="J480" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>46384</v>
       </c>
       <c r="B481" t="n">
@@ -18706,14 +17760,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
       <c r="J481" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="B482" t="n">
@@ -18744,14 +17796,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
       <c r="J482" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="B483" t="n">
@@ -18782,14 +17832,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
       <c r="J483" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B484" t="n">
@@ -18820,14 +17868,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
       <c r="J484" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B485" t="n">
@@ -18858,14 +17904,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
       <c r="J485" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B486" t="n">
@@ -18896,14 +17940,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
       <c r="J486" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B487" t="n">
@@ -18934,14 +17976,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
       <c r="J487" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B488" t="n">
@@ -18972,14 +18012,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
-      <c r="I488" t="inlineStr"/>
       <c r="J488" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B489" t="n">
@@ -19010,14 +18048,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr"/>
-      <c r="I489" t="inlineStr"/>
       <c r="J489" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B490" t="n">
@@ -19048,14 +18084,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
-      <c r="I490" t="inlineStr"/>
       <c r="J490" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B491" t="n">
@@ -19086,14 +18120,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr"/>
       <c r="J491" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B492" t="n">
@@ -19124,14 +18156,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
-      <c r="I492" t="inlineStr"/>
       <c r="J492" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B493" t="n">
@@ -19162,14 +18192,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
-      <c r="I493" t="inlineStr"/>
       <c r="J493" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B494" t="n">
@@ -19200,14 +18228,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
       <c r="J494" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B495" t="n">
@@ -19238,14 +18264,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
       <c r="J495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B496" t="n">
@@ -19276,14 +18300,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr"/>
-      <c r="I496" t="inlineStr"/>
       <c r="J496" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B497" t="n">
@@ -19314,14 +18336,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr"/>
-      <c r="I497" t="inlineStr"/>
       <c r="J497" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B498" t="n">
@@ -19352,14 +18372,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
-      <c r="I498" t="inlineStr"/>
       <c r="J498" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B499" t="n">
@@ -19390,14 +18408,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
       <c r="J499" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B500" t="n">
@@ -19428,14 +18444,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
       <c r="J500" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B501" t="n">
@@ -19466,14 +18480,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
-      <c r="I501" t="inlineStr"/>
       <c r="J501" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B502" t="n">
@@ -19504,14 +18516,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
       <c r="J502" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B503" t="n">
@@ -19542,14 +18552,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr"/>
       <c r="J503" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B504" t="n">
@@ -19580,14 +18588,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
       <c r="J504" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B505" t="n">
@@ -19618,14 +18624,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
       <c r="J505" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B506" t="n">
@@ -19656,14 +18660,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr"/>
-      <c r="I506" t="inlineStr"/>
       <c r="J506" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B507" t="n">
@@ -19694,14 +18696,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
-      <c r="I507" t="inlineStr"/>
       <c r="J507" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B508" t="n">
@@ -19732,14 +18732,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr"/>
-      <c r="I508" t="inlineStr"/>
       <c r="J508" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B509" t="n">
@@ -19770,14 +18768,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr"/>
-      <c r="I509" t="inlineStr"/>
       <c r="J509" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B510" t="n">
@@ -19808,14 +18804,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr"/>
-      <c r="I510" t="inlineStr"/>
       <c r="J510" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="B511" t="n">
@@ -19846,14 +18840,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr"/>
       <c r="J511" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>46391</v>
       </c>
       <c r="B512" t="n">
@@ -19884,14 +18876,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr"/>
-      <c r="I512" t="inlineStr"/>
       <c r="J512" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>46391</v>
       </c>
       <c r="B513" t="n">
@@ -19922,14 +18912,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
       <c r="J513" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B514" t="n">
@@ -19960,14 +18948,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr"/>
       <c r="J514" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B515" t="n">
@@ -19998,14 +18984,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr"/>
       <c r="J515" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B516" t="n">
@@ -20036,14 +19020,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr"/>
-      <c r="I516" t="inlineStr"/>
       <c r="J516" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B517" t="n">
@@ -20074,14 +19056,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
       <c r="J517" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B518" t="n">
@@ -20112,14 +19092,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr"/>
-      <c r="I518" t="inlineStr"/>
       <c r="J518" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B519" t="n">
@@ -20150,14 +19128,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr"/>
-      <c r="I519" t="inlineStr"/>
       <c r="J519" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B520" t="n">
@@ -20188,14 +19164,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr"/>
-      <c r="I520" t="inlineStr"/>
       <c r="J520" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B521" t="n">
@@ -20226,14 +19200,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
       <c r="J521" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B522" t="n">
@@ -20264,14 +19236,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr"/>
-      <c r="I522" t="inlineStr"/>
       <c r="J522" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B523" t="n">
@@ -20302,14 +19272,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr"/>
       <c r="J523" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B524" t="n">
@@ -20340,14 +19308,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr"/>
-      <c r="I524" t="inlineStr"/>
       <c r="J524" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B525" t="n">
@@ -20378,14 +19344,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr"/>
       <c r="J525" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B526" t="n">
@@ -20416,14 +19380,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr"/>
-      <c r="I526" t="inlineStr"/>
       <c r="J526" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B527" t="n">
@@ -20454,14 +19416,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr"/>
       <c r="J527" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B528" t="n">
@@ -20492,14 +19452,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr"/>
-      <c r="I528" t="inlineStr"/>
       <c r="J528" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B529" t="n">
@@ -20530,14 +19488,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr"/>
-      <c r="I529" t="inlineStr"/>
       <c r="J529" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B530" t="n">
@@ -20568,14 +19524,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr"/>
-      <c r="I530" t="inlineStr"/>
       <c r="J530" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B531" t="n">
@@ -20606,14 +19560,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr"/>
       <c r="J531" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B532" t="n">
@@ -20644,14 +19596,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr"/>
-      <c r="I532" t="inlineStr"/>
       <c r="J532" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B533" t="n">
@@ -20682,14 +19632,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr"/>
-      <c r="I533" t="inlineStr"/>
       <c r="J533" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B534" t="n">
@@ -20720,14 +19668,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr"/>
-      <c r="I534" t="inlineStr"/>
       <c r="J534" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B535" t="n">
@@ -20758,14 +19704,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr"/>
-      <c r="I535" t="inlineStr"/>
       <c r="J535" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B536" t="n">
@@ -20796,14 +19740,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr"/>
-      <c r="I536" t="inlineStr"/>
       <c r="J536" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B537" t="n">
@@ -20834,14 +19776,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr"/>
-      <c r="I537" t="inlineStr"/>
       <c r="J537" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B538" t="n">
@@ -20872,14 +19812,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr"/>
-      <c r="I538" t="inlineStr"/>
       <c r="J538" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B539" t="n">
@@ -20910,14 +19848,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr"/>
-      <c r="I539" t="inlineStr"/>
       <c r="J539" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B540" t="n">
@@ -20948,14 +19884,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr"/>
-      <c r="I540" t="inlineStr"/>
       <c r="J540" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B541" t="n">
@@ -20986,14 +19920,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr"/>
-      <c r="I541" t="inlineStr"/>
       <c r="J541" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B542" t="n">
@@ -21024,14 +19956,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr"/>
       <c r="J542" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B543" t="n">
@@ -21062,14 +19992,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr"/>
       <c r="J543" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B544" t="n">
@@ -21100,14 +20028,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr"/>
-      <c r="I544" t="inlineStr"/>
       <c r="J544" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>46397</v>
       </c>
       <c r="B545" t="n">
@@ -21138,8 +20064,6 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr"/>
-      <c r="I545" t="inlineStr"/>
       <c r="J545" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -673,8 +673,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
+      <c r="H6" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
@@ -711,8 +715,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n"/>
-      <c r="I7" s="1" t="n"/>
+      <c r="H7" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J7" s="1" t="n">
         <v>0</v>
       </c>
@@ -749,8 +757,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n"/>
-      <c r="I8" s="1" t="n"/>
+      <c r="H8" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J8" s="1" t="n">
         <v>0</v>
       </c>
@@ -787,8 +799,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
+      <c r="H9" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J9" s="1" t="n">
         <v>0</v>
       </c>
@@ -825,8 +841,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n"/>
-      <c r="I10" s="1" t="n"/>
+      <c r="H10" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>41</v>
+      </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
@@ -863,8 +883,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
+      <c r="H11" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J11" s="1" t="n">
         <v>0</v>
       </c>
@@ -901,8 +925,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
+      <c r="H12" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="J12" s="1" t="n">
         <v>0</v>
       </c>
@@ -939,8 +967,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
+      <c r="H13" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J13" s="1" t="n">
         <v>0</v>
       </c>
@@ -977,8 +1009,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
+      <c r="H14" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>59</v>
+      </c>
       <c r="J14" s="1" t="n">
         <v>0</v>
       </c>
@@ -1015,8 +1051,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
+      <c r="H15" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>37</v>
+      </c>
       <c r="J15" s="1" t="n">
         <v>0</v>
       </c>
@@ -1053,8 +1093,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
+      <c r="H16" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J16" s="1" t="n">
         <v>0</v>
       </c>
@@ -1091,8 +1135,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n"/>
-      <c r="I17" s="1" t="n"/>
+      <c r="H17" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="J17" s="1" t="n">
         <v>0</v>
       </c>
@@ -1129,8 +1177,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
+      <c r="H18" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J18" s="1" t="n">
         <v>0</v>
       </c>
@@ -1167,8 +1219,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n"/>
-      <c r="I19" s="1" t="n"/>
+      <c r="H19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J19" s="1" t="n">
         <v>0</v>
       </c>
@@ -1281,10 +1337,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n"/>
-      <c r="I22" s="1" t="n"/>
+      <c r="H22" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J22" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="15.5" customHeight="1">
@@ -1319,10 +1379,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
+      <c r="H23" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J23" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="15.5" customHeight="1">
@@ -1433,8 +1497,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n"/>
-      <c r="I26" s="1" t="n"/>
+      <c r="H26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J26" s="1" t="n">
         <v>0</v>
       </c>
@@ -1471,8 +1539,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
+      <c r="H27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J27" s="1" t="n">
         <v>0</v>
       </c>
@@ -1509,8 +1581,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
+      <c r="H28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J28" s="1" t="n">
         <v>0</v>
       </c>
@@ -1547,8 +1623,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n"/>
-      <c r="I29" s="1" t="n"/>
+      <c r="H29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J29" s="1" t="n">
         <v>0</v>
       </c>
@@ -1585,8 +1665,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="1" t="n"/>
+      <c r="H30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>22</v>
+      </c>
       <c r="J30" s="1" t="n">
         <v>0</v>
       </c>
@@ -1623,8 +1707,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
+      <c r="H31" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J31" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -1421,8 +1421,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
+      <c r="H24" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>22</v>
+      </c>
       <c r="J24" s="1" t="n">
         <v>0</v>
       </c>
@@ -1459,8 +1463,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n"/>
-      <c r="I25" s="1" t="n"/>
+      <c r="H25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>39</v>
+      </c>
       <c r="J25" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -1261,8 +1261,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
+      <c r="H20" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J20" s="1" t="n">
         <v>0</v>
       </c>
@@ -1299,8 +1303,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
+      <c r="H21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>28</v>
+      </c>
       <c r="J21" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -1765,8 +1765,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
+      <c r="H32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J32" s="1" t="n">
         <v>0</v>
       </c>
@@ -1803,8 +1807,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n"/>
-      <c r="I33" s="1" t="n"/>
+      <c r="H33" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J33" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -1849,8 +1849,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H34" s="1" t="n"/>
-      <c r="I34" s="1" t="n"/>
+      <c r="H34" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J34" s="1" t="n">
         <v>0</v>
       </c>
@@ -1887,8 +1891,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H35" s="1" t="n"/>
-      <c r="I35" s="1" t="n"/>
+      <c r="H35" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>41</v>
+      </c>
       <c r="J35" s="1" t="n">
         <v>0</v>
       </c>
@@ -1925,8 +1933,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H36" s="1" t="n"/>
-      <c r="I36" s="1" t="n"/>
+      <c r="H36" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J36" s="1" t="n">
         <v>0</v>
       </c>
@@ -1963,8 +1975,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H37" s="1" t="n"/>
-      <c r="I37" s="1" t="n"/>
+      <c r="H37" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="J37" s="1" t="n">
         <v>0</v>
       </c>
@@ -2001,8 +2017,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
+      <c r="H38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J38" s="1" t="n">
         <v>0</v>
       </c>
@@ -2039,8 +2059,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H39" s="1" t="n"/>
-      <c r="I39" s="1" t="n"/>
+      <c r="H39" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="J39" s="1" t="n">
         <v>0</v>
       </c>
@@ -2077,8 +2101,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H40" s="1" t="n"/>
-      <c r="I40" s="1" t="n"/>
+      <c r="H40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J40" s="1" t="n">
         <v>0</v>
       </c>
@@ -2115,8 +2143,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H41" s="1" t="n"/>
-      <c r="I41" s="1" t="n"/>
+      <c r="H41" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J41" s="1" t="n">
         <v>0</v>
       </c>
@@ -2153,8 +2185,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H42" s="1" t="n"/>
-      <c r="I42" s="1" t="n"/>
+      <c r="H42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="J42" s="1" t="n">
         <v>0</v>
       </c>
@@ -2191,8 +2227,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
+      <c r="H43" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="J43" s="1" t="n">
         <v>0</v>
       </c>
@@ -2229,8 +2269,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H44" s="1" t="n"/>
-      <c r="I44" s="1" t="n"/>
+      <c r="H44" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J44" s="1" t="n">
         <v>0</v>
       </c>
@@ -2267,8 +2311,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H45" s="1" t="n"/>
-      <c r="I45" s="1" t="n"/>
+      <c r="H45" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J45" s="1" t="n">
         <v>0</v>
       </c>
@@ -2305,8 +2353,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="n"/>
+      <c r="H46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J46" s="1" t="n">
         <v>0</v>
       </c>
@@ -2343,8 +2395,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H47" s="1" t="n"/>
-      <c r="I47" s="1" t="n"/>
+      <c r="H47" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J47" s="1" t="n">
         <v>0</v>
       </c>
@@ -2381,8 +2437,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H48" s="1" t="n"/>
-      <c r="I48" s="1" t="n"/>
+      <c r="H48" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J48" s="1" t="n">
         <v>0</v>
       </c>
@@ -2419,8 +2479,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H49" s="1" t="n"/>
-      <c r="I49" s="1" t="n"/>
+      <c r="H49" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>37</v>
+      </c>
       <c r="J49" s="1" t="n">
         <v>0</v>
       </c>
@@ -2457,8 +2521,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H50" s="1" t="n"/>
-      <c r="I50" s="1" t="n"/>
+      <c r="H50" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J50" s="1" t="n">
         <v>0</v>
       </c>
@@ -2495,8 +2563,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H51" s="1" t="n"/>
-      <c r="I51" s="1" t="n"/>
+      <c r="H51" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J51" s="1" t="n">
         <v>0</v>
       </c>
@@ -2533,10 +2605,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H52" s="1" t="n"/>
-      <c r="I52" s="1" t="n"/>
+      <c r="H52" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J52" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -2571,10 +2647,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
+      <c r="H53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J53" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -2609,10 +2689,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
+      <c r="H54" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J54" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="15.5" customHeight="1">
@@ -2647,10 +2731,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H55" s="1" t="n"/>
-      <c r="I55" s="1" t="n"/>
+      <c r="H55" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="J55" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -2685,8 +2773,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H56" s="1" t="n"/>
-      <c r="I56" s="1" t="n"/>
+      <c r="H56" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J56" s="1" t="n">
         <v>0</v>
       </c>
@@ -2723,8 +2815,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H57" s="1" t="n"/>
-      <c r="I57" s="1" t="n"/>
+      <c r="H57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J57" s="1" t="n">
         <v>0</v>
       </c>
@@ -2761,8 +2857,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H58" s="1" t="n"/>
-      <c r="I58" s="1" t="n"/>
+      <c r="H58" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="J58" s="1" t="n">
         <v>0</v>
       </c>
@@ -2799,8 +2899,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
+      <c r="H59" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J59" s="1" t="n">
         <v>0</v>
       </c>
@@ -2837,8 +2941,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H60" s="1" t="n"/>
-      <c r="I60" s="1" t="n"/>
+      <c r="H60" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J60" s="1" t="n">
         <v>0</v>
       </c>
@@ -2875,8 +2983,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H61" s="1" t="n"/>
-      <c r="I61" s="1" t="n"/>
+      <c r="H61" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J61" s="1" t="n">
         <v>0</v>
       </c>
@@ -2913,8 +3025,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H62" s="1" t="n"/>
-      <c r="I62" s="1" t="n"/>
+      <c r="H62" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J62" s="1" t="n">
         <v>0</v>
       </c>
@@ -2951,8 +3067,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H63" s="1" t="n"/>
-      <c r="I63" s="1" t="n"/>
+      <c r="H63" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J63" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -3109,8 +3109,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H64" s="1" t="n"/>
-      <c r="I64" s="1" t="n"/>
+      <c r="H64" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J64" s="1" t="n">
         <v>0</v>
       </c>
@@ -3147,8 +3151,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H65" s="1" t="n"/>
-      <c r="I65" s="1" t="n"/>
+      <c r="H65" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>28</v>
+      </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
@@ -3185,8 +3193,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H66" s="1" t="n"/>
-      <c r="I66" s="1" t="n"/>
+      <c r="H66" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
@@ -3223,8 +3235,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H67" s="1" t="n"/>
-      <c r="I67" s="1" t="n"/>
+      <c r="H67" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -3277,8 +3277,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H68" s="1" t="n"/>
-      <c r="I68" s="1" t="n"/>
+      <c r="H68" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
       </c>
@@ -3315,8 +3319,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H69" s="1" t="n"/>
-      <c r="I69" s="1" t="n"/>
+      <c r="H69" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="J69" s="1" t="n">
         <v>0</v>
       </c>
@@ -3353,8 +3361,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H70" s="1" t="n"/>
-      <c r="I70" s="1" t="n"/>
+      <c r="H70" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J70" s="1" t="n">
         <v>0</v>
       </c>
@@ -3391,8 +3403,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H71" s="1" t="n"/>
-      <c r="I71" s="1" t="n"/>
+      <c r="H71" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J71" s="1" t="n">
         <v>0</v>
       </c>
@@ -3429,8 +3445,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H72" s="1" t="n"/>
-      <c r="I72" s="1" t="n"/>
+      <c r="H72" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J72" s="1" t="n">
         <v>0</v>
       </c>
@@ -3467,8 +3487,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H73" s="1" t="n"/>
-      <c r="I73" s="1" t="n"/>
+      <c r="H73" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J73" s="1" t="n">
         <v>0</v>
       </c>
@@ -3505,8 +3529,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H74" s="1" t="n"/>
-      <c r="I74" s="1" t="n"/>
+      <c r="H74" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>18</v>
+      </c>
       <c r="J74" s="1" t="n">
         <v>0</v>
       </c>
@@ -3543,8 +3571,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
+      <c r="H75" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="J75" s="1" t="n">
         <v>0</v>
       </c>
@@ -3581,8 +3613,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H76" s="1" t="n"/>
-      <c r="I76" s="1" t="n"/>
+      <c r="H76" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J76" s="1" t="n">
         <v>0</v>
       </c>
@@ -3619,8 +3655,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H77" s="1" t="n"/>
-      <c r="I77" s="1" t="n"/>
+      <c r="H77" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J77" s="1" t="n">
         <v>0</v>
       </c>
@@ -3657,8 +3697,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H78" s="1" t="n"/>
-      <c r="I78" s="1" t="n"/>
+      <c r="H78" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J78" s="1" t="n">
         <v>0</v>
       </c>
@@ -3695,8 +3739,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H79" s="1" t="n"/>
-      <c r="I79" s="1" t="n"/>
+      <c r="H79" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J79" s="1" t="n">
         <v>0</v>
       </c>
@@ -3733,8 +3781,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H80" s="1" t="n"/>
-      <c r="I80" s="1" t="n"/>
+      <c r="H80" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J80" s="1" t="n">
         <v>0</v>
       </c>
@@ -3771,8 +3823,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H81" s="1" t="n"/>
-      <c r="I81" s="1" t="n"/>
+      <c r="H81" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J81" s="1" t="n">
         <v>0</v>
       </c>
@@ -3809,8 +3865,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H82" s="1" t="n"/>
-      <c r="I82" s="1" t="n"/>
+      <c r="H82" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J82" s="1" t="n">
         <v>0</v>
       </c>
@@ -3847,8 +3907,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H83" s="1" t="n"/>
-      <c r="I83" s="1" t="n"/>
+      <c r="H83" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J83" s="1" t="n">
         <v>0</v>
       </c>
@@ -3885,8 +3949,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H84" s="1" t="n"/>
-      <c r="I84" s="1" t="n"/>
+      <c r="H84" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J84" s="1" t="n">
         <v>0</v>
       </c>
@@ -3923,8 +3991,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H85" s="1" t="n"/>
-      <c r="I85" s="1" t="n"/>
+      <c r="H85" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J85" s="1" t="n">
         <v>0</v>
       </c>
@@ -3961,8 +4033,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H86" s="1" t="n"/>
-      <c r="I86" s="1" t="n"/>
+      <c r="H86" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J86" s="1" t="n">
         <v>0</v>
       </c>
@@ -3999,8 +4075,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H87" s="1" t="n"/>
-      <c r="I87" s="1" t="n"/>
+      <c r="H87" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J87" s="1" t="n">
         <v>0</v>
       </c>
@@ -4037,8 +4117,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H88" s="1" t="n"/>
-      <c r="I88" s="1" t="n"/>
+      <c r="H88" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J88" s="1" t="n">
         <v>0</v>
       </c>
@@ -4075,8 +4159,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H89" s="1" t="n"/>
-      <c r="I89" s="1" t="n"/>
+      <c r="H89" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J89" s="1" t="n">
         <v>0</v>
       </c>
@@ -4113,8 +4201,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H90" s="1" t="n"/>
-      <c r="I90" s="1" t="n"/>
+      <c r="H90" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J90" s="1" t="n">
         <v>0</v>
       </c>
@@ -4151,8 +4243,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H91" s="1" t="n"/>
-      <c r="I91" s="1" t="n"/>
+      <c r="H91" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J91" s="1" t="n">
         <v>0</v>
       </c>
@@ -4189,8 +4285,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H92" s="1" t="n"/>
-      <c r="I92" s="1" t="n"/>
+      <c r="H92" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="J92" s="1" t="n">
         <v>0</v>
       </c>
@@ -4227,8 +4327,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H93" s="1" t="n"/>
-      <c r="I93" s="1" t="n"/>
+      <c r="H93" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="J93" s="1" t="n">
         <v>0</v>
       </c>
@@ -4265,8 +4369,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H94" s="1" t="n"/>
-      <c r="I94" s="1" t="n"/>
+      <c r="H94" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J94" s="1" t="n">
         <v>0</v>
       </c>
@@ -4303,8 +4411,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H95" s="1" t="n"/>
-      <c r="I95" s="1" t="n"/>
+      <c r="H95" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="J95" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -4453,8 +4453,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H96" s="1" t="n"/>
-      <c r="I96" s="1" t="n"/>
+      <c r="H96" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="J96" s="1" t="n">
         <v>0</v>
       </c>
@@ -4491,8 +4495,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H97" s="1" t="n"/>
-      <c r="I97" s="1" t="n"/>
+      <c r="H97" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J97" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -4537,8 +4537,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H98" s="1" t="n"/>
-      <c r="I98" s="1" t="n"/>
+      <c r="H98" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J98" s="1" t="n">
         <v>0</v>
       </c>
@@ -4575,8 +4579,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H99" s="1" t="n"/>
-      <c r="I99" s="1" t="n"/>
+      <c r="H99" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J99" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -4621,8 +4621,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H100" s="1" t="n"/>
-      <c r="I100" s="1" t="n"/>
+      <c r="H100" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J100" s="1" t="n">
         <v>0</v>
       </c>
@@ -4659,8 +4663,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H101" s="1" t="n"/>
-      <c r="I101" s="1" t="n"/>
+      <c r="H101" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="J101" s="1" t="n">
         <v>0</v>
       </c>
@@ -4697,8 +4705,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H102" s="1" t="n"/>
-      <c r="I102" s="1" t="n"/>
+      <c r="H102" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>18</v>
+      </c>
       <c r="J102" s="1" t="n">
         <v>0</v>
       </c>
@@ -4735,8 +4747,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H103" s="1" t="n"/>
-      <c r="I103" s="1" t="n"/>
+      <c r="H103" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J103" s="1" t="n">
         <v>0</v>
       </c>
@@ -4773,8 +4789,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H104" s="1" t="n"/>
-      <c r="I104" s="1" t="n"/>
+      <c r="H104" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>29</v>
+      </c>
       <c r="J104" s="1" t="n">
         <v>0</v>
       </c>
@@ -4811,8 +4831,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H105" s="1" t="n"/>
-      <c r="I105" s="1" t="n"/>
+      <c r="H105" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J105" s="1" t="n">
         <v>0</v>
       </c>
@@ -4849,8 +4873,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H106" s="1" t="n"/>
-      <c r="I106" s="1" t="n"/>
+      <c r="H106" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J106" s="1" t="n">
         <v>0</v>
       </c>
@@ -4887,8 +4915,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H107" s="1" t="n"/>
-      <c r="I107" s="1" t="n"/>
+      <c r="H107" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="J107" s="1" t="n">
         <v>0</v>
       </c>
@@ -4925,8 +4957,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H108" s="1" t="n"/>
-      <c r="I108" s="1" t="n"/>
+      <c r="H108" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="J108" s="1" t="n">
         <v>0</v>
       </c>
@@ -4963,8 +4999,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H109" s="1" t="n"/>
-      <c r="I109" s="1" t="n"/>
+      <c r="H109" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J109" s="1" t="n">
         <v>0</v>
       </c>
@@ -5001,8 +5041,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H110" s="1" t="n"/>
-      <c r="I110" s="1" t="n"/>
+      <c r="H110" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>22</v>
+      </c>
       <c r="J110" s="1" t="n">
         <v>0</v>
       </c>
@@ -5039,8 +5083,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H111" s="1" t="n"/>
-      <c r="I111" s="1" t="n"/>
+      <c r="H111" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J111" s="1" t="n">
         <v>0</v>
       </c>
@@ -5077,8 +5125,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H112" s="1" t="n"/>
-      <c r="I112" s="1" t="n"/>
+      <c r="H112" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J112" s="1" t="n">
         <v>0</v>
       </c>
@@ -5115,8 +5167,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H113" s="1" t="n"/>
-      <c r="I113" s="1" t="n"/>
+      <c r="H113" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J113" s="1" t="n">
         <v>0</v>
       </c>
@@ -5153,8 +5209,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H114" s="1" t="n"/>
-      <c r="I114" s="1" t="n"/>
+      <c r="H114" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J114" s="1" t="n">
         <v>0</v>
       </c>
@@ -5191,8 +5251,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H115" s="1" t="n"/>
-      <c r="I115" s="1" t="n"/>
+      <c r="H115" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J115" s="1" t="n">
         <v>0</v>
       </c>
@@ -5229,8 +5293,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H116" s="1" t="n"/>
-      <c r="I116" s="1" t="n"/>
+      <c r="H116" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J116" s="1" t="n">
         <v>0</v>
       </c>
@@ -5267,8 +5335,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H117" s="1" t="n"/>
-      <c r="I117" s="1" t="n"/>
+      <c r="H117" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J117" s="1" t="n">
         <v>0</v>
       </c>
@@ -5305,8 +5377,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H118" s="1" t="n"/>
-      <c r="I118" s="1" t="n"/>
+      <c r="H118" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J118" s="1" t="n">
         <v>0</v>
       </c>
@@ -5343,8 +5419,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H119" s="1" t="n"/>
-      <c r="I119" s="1" t="n"/>
+      <c r="H119" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J119" s="1" t="n">
         <v>0</v>
       </c>
@@ -5381,8 +5461,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H120" s="1" t="n"/>
-      <c r="I120" s="1" t="n"/>
+      <c r="H120" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J120" s="1" t="n">
         <v>0</v>
       </c>
@@ -5419,8 +5503,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H121" s="1" t="n"/>
-      <c r="I121" s="1" t="n"/>
+      <c r="H121" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J121" s="1" t="n">
         <v>0</v>
       </c>
@@ -5457,8 +5545,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H122" s="1" t="n"/>
-      <c r="I122" s="1" t="n"/>
+      <c r="H122" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J122" s="1" t="n">
         <v>0</v>
       </c>
@@ -5495,8 +5587,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H123" s="1" t="n"/>
-      <c r="I123" s="1" t="n"/>
+      <c r="H123" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>15</v>
+      </c>
       <c r="J123" s="1" t="n">
         <v>0</v>
       </c>
@@ -5533,8 +5629,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H124" s="1" t="n"/>
-      <c r="I124" s="1" t="n"/>
+      <c r="H124" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J124" s="1" t="n">
         <v>0</v>
       </c>
@@ -5571,8 +5671,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H125" s="1" t="n"/>
-      <c r="I125" s="1" t="n"/>
+      <c r="H125" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J125" s="1" t="n">
         <v>0</v>
       </c>
@@ -5609,8 +5713,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H126" s="1" t="n"/>
-      <c r="I126" s="1" t="n"/>
+      <c r="H126" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J126" s="1" t="n">
         <v>0</v>
       </c>
@@ -5647,8 +5755,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H127" s="1" t="n"/>
-      <c r="I127" s="1" t="n"/>
+      <c r="H127" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J127" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -5797,8 +5797,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H128" s="1" t="n"/>
-      <c r="I128" s="1" t="n"/>
+      <c r="H128" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>45</v>
+      </c>
       <c r="J128" s="1" t="n">
         <v>0</v>
       </c>
@@ -5835,8 +5839,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H129" s="1" t="n"/>
-      <c r="I129" s="1" t="n"/>
+      <c r="H129" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J129" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -5881,8 +5881,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H130" s="1" t="n"/>
-      <c r="I130" s="1" t="n"/>
+      <c r="H130" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J130" s="1" t="n">
         <v>0</v>
       </c>
@@ -5919,8 +5923,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H131" s="1" t="n"/>
-      <c r="I131" s="1" t="n"/>
+      <c r="H131" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J131" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFL_2026_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NFL_2026_Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -6117,8 +6117,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H136" s="1" t="n"/>
-      <c r="I136" s="1" t="n"/>
+      <c r="H136" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I136" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="J136" s="1" t="n">
         <v>0</v>
       </c>
@@ -6155,8 +6159,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H137" s="1" t="n"/>
-      <c r="I137" s="1" t="n"/>
+      <c r="H137" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I137" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J137" s="1" t="n">
         <v>0</v>
       </c>
@@ -6193,8 +6201,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H138" s="1" t="n"/>
-      <c r="I138" s="1" t="n"/>
+      <c r="H138" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I138" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J138" s="1" t="n">
         <v>0</v>
       </c>
@@ -6231,8 +6243,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H139" s="1" t="n"/>
-      <c r="I139" s="1" t="n"/>
+      <c r="H139" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I139" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J139" s="1" t="n">
         <v>0</v>
       </c>
@@ -6269,8 +6285,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H140" s="1" t="n"/>
-      <c r="I140" s="1" t="n"/>
+      <c r="H140" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I140" s="1" t="n">
+        <v>12</v>
+      </c>
       <c r="J140" s="1" t="n">
         <v>0</v>
       </c>
@@ -6307,8 +6327,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H141" s="1" t="n"/>
-      <c r="I141" s="1" t="n"/>
+      <c r="H141" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I141" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J141" s="1" t="n">
         <v>0</v>
       </c>
@@ -6421,8 +6445,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H144" s="1" t="n"/>
-      <c r="I144" s="1" t="n"/>
+      <c r="H144" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I144" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J144" s="1" t="n">
         <v>0</v>
       </c>
@@ -6459,8 +6487,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H145" s="1" t="n"/>
-      <c r="I145" s="1" t="n"/>
+      <c r="H145" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I145" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="J145" s="1" t="n">
         <v>0</v>
       </c>
@@ -6497,8 +6529,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H146" s="1" t="n"/>
-      <c r="I146" s="1" t="n"/>
+      <c r="H146" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I146" s="1" t="n">
+        <v>22</v>
+      </c>
       <c r="J146" s="1" t="n">
         <v>0</v>
       </c>
@@ -6535,8 +6571,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H147" s="1" t="n"/>
-      <c r="I147" s="1" t="n"/>
+      <c r="H147" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I147" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J147" s="1" t="n">
         <v>0</v>
       </c>
@@ -6573,8 +6613,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H148" s="1" t="n"/>
-      <c r="I148" s="1" t="n"/>
+      <c r="H148" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I148" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J148" s="1" t="n">
         <v>0</v>
       </c>
@@ -6611,8 +6655,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H149" s="1" t="n"/>
-      <c r="I149" s="1" t="n"/>
+      <c r="H149" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I149" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J149" s="1" t="n">
         <v>0</v>
       </c>
@@ -6649,8 +6697,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H150" s="1" t="n"/>
-      <c r="I150" s="1" t="n"/>
+      <c r="H150" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I150" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J150" s="1" t="n">
         <v>0</v>
       </c>
@@ -6687,8 +6739,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H151" s="1" t="n"/>
-      <c r="I151" s="1" t="n"/>
+      <c r="H151" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I151" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J151" s="1" t="n">
         <v>0</v>
       </c>
@@ -6725,8 +6781,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H152" s="1" t="n"/>
-      <c r="I152" s="1" t="n"/>
+      <c r="H152" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="I152" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J152" s="1" t="n">
         <v>0</v>
       </c>
@@ -6763,8 +6823,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H153" s="1" t="n"/>
-      <c r="I153" s="1" t="n"/>
+      <c r="H153" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I153" s="1" t="n">
+        <v>45</v>
+      </c>
       <c r="J153" s="1" t="n">
         <v>0</v>
       </c>
@@ -6801,10 +6865,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H154" s="1" t="n"/>
-      <c r="I154" s="1" t="n"/>
+      <c r="H154" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I154" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J154" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" ht="15.5" customHeight="1">
@@ -6839,10 +6907,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H155" s="1" t="n"/>
-      <c r="I155" s="1" t="n"/>
+      <c r="H155" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I155" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J155" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" ht="15.5" customHeight="1">

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -5965,8 +5965,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H132" s="1" t="n"/>
-      <c r="I132" s="1" t="n"/>
+      <c r="H132" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>45</v>
+      </c>
       <c r="J132" s="1" t="n">
         <v>0</v>
       </c>
@@ -6003,8 +6007,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
+      <c r="H133" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="J133" s="1" t="n">
         <v>0</v>
       </c>
@@ -6369,8 +6377,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H142" s="1" t="n"/>
-      <c r="I142" s="1" t="n"/>
+      <c r="H142" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I142" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J142" s="1" t="n">
         <v>0</v>
       </c>
@@ -6407,8 +6419,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H143" s="1" t="n"/>
-      <c r="I143" s="1" t="n"/>
+      <c r="H143" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I143" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J143" s="1" t="n">
         <v>0</v>
       </c>
@@ -6949,8 +6965,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H156" s="1" t="n"/>
-      <c r="I156" s="1" t="n"/>
+      <c r="H156" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I156" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="J156" s="1" t="n">
         <v>0</v>
       </c>
@@ -6987,8 +7007,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H157" s="1" t="n"/>
-      <c r="I157" s="1" t="n"/>
+      <c r="H157" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="I157" s="1" t="n">
+        <v>29</v>
+      </c>
       <c r="J157" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -6049,10 +6049,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H134" s="1" t="n"/>
-      <c r="I134" s="1" t="n"/>
+      <c r="H134" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J134" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" ht="15.5" customHeight="1">
@@ -6087,10 +6091,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H135" s="1" t="n"/>
-      <c r="I135" s="1" t="n"/>
+      <c r="H135" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J135" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" ht="15.5" customHeight="1">

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7057,10 +7057,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H158" s="1" t="n"/>
-      <c r="I158" s="1" t="n"/>
+      <c r="H158" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I158" s="1" t="n">
+        <v>37</v>
+      </c>
       <c r="J158" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" ht="15.5" customHeight="1">
@@ -7095,10 +7099,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H159" s="1" t="n"/>
-      <c r="I159" s="1" t="n"/>
+      <c r="H159" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J159" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" ht="15.5" customHeight="1">

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7141,10 +7141,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H160" s="1" t="n"/>
-      <c r="I160" s="1" t="n"/>
+      <c r="H160" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J160" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" ht="15.5" customHeight="1">
@@ -7179,10 +7183,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H161" s="1" t="n"/>
-      <c r="I161" s="1" t="n"/>
+      <c r="H161" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I161" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J161" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" ht="15.5" customHeight="1">

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7681,8 +7681,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H174" s="1" t="n"/>
-      <c r="I174" s="1" t="n"/>
+      <c r="H174" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I174" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J174" s="1" t="n">
         <v>0</v>
       </c>
@@ -7719,8 +7723,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H175" s="1" t="n"/>
-      <c r="I175" s="1" t="n"/>
+      <c r="H175" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I175" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J175" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7301,8 +7301,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H164" s="1" t="n"/>
-      <c r="I164" s="1" t="n"/>
+      <c r="H164" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I164" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="J164" s="1" t="n">
         <v>0</v>
       </c>
@@ -7339,8 +7343,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H165" s="1" t="n"/>
-      <c r="I165" s="1" t="n"/>
+      <c r="H165" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I165" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J165" s="1" t="n">
         <v>0</v>
       </c>
@@ -7377,8 +7385,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H166" s="1" t="n"/>
-      <c r="I166" s="1" t="n"/>
+      <c r="H166" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I166" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J166" s="1" t="n">
         <v>0</v>
       </c>
@@ -7415,8 +7427,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H167" s="1" t="n"/>
-      <c r="I167" s="1" t="n"/>
+      <c r="H167" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I167" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J167" s="1" t="n">
         <v>0</v>
       </c>
@@ -7765,8 +7781,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H176" s="1" t="n"/>
-      <c r="I176" s="1" t="n"/>
+      <c r="H176" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I176" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J176" s="1" t="n">
         <v>0</v>
       </c>
@@ -7803,8 +7823,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H177" s="1" t="n"/>
-      <c r="I177" s="1" t="n"/>
+      <c r="H177" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I177" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J177" s="1" t="n">
         <v>0</v>
       </c>
@@ -7917,8 +7941,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H180" s="1" t="n"/>
-      <c r="I180" s="1" t="n"/>
+      <c r="H180" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I180" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J180" s="1" t="n">
         <v>0</v>
       </c>
@@ -7955,8 +7983,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H181" s="1" t="n"/>
-      <c r="I181" s="1" t="n"/>
+      <c r="H181" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I181" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J181" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7545,8 +7545,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H170" s="1" t="n"/>
-      <c r="I170" s="1" t="n"/>
+      <c r="H170" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I170" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="J170" s="1" t="n">
         <v>0</v>
       </c>
@@ -7583,8 +7587,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H171" s="1" t="n"/>
-      <c r="I171" s="1" t="n"/>
+      <c r="H171" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I171" s="1" t="n">
+        <v>14</v>
+      </c>
       <c r="J171" s="1" t="n">
         <v>0</v>
       </c>
@@ -8025,8 +8033,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H182" s="1" t="n"/>
-      <c r="I182" s="1" t="n"/>
+      <c r="H182" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I182" s="1" t="n">
+        <v>34</v>
+      </c>
       <c r="J182" s="1" t="n">
         <v>0</v>
       </c>
@@ -8063,8 +8075,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H183" s="1" t="n"/>
-      <c r="I183" s="1" t="n"/>
+      <c r="H183" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I183" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J183" s="1" t="n">
         <v>0</v>
       </c>
@@ -8101,10 +8117,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H184" s="1" t="n"/>
-      <c r="I184" s="1" t="n"/>
+      <c r="H184" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I184" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="J184" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" ht="15.5" customHeight="1">
@@ -8139,10 +8159,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H185" s="1" t="n"/>
-      <c r="I185" s="1" t="n"/>
+      <c r="H185" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I185" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J185" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" ht="15.5" customHeight="1">

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7225,8 +7225,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H162" s="1" t="n"/>
-      <c r="I162" s="1" t="n"/>
+      <c r="H162" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I162" s="1" t="n">
+        <v>18</v>
+      </c>
       <c r="J162" s="1" t="n">
         <v>0</v>
       </c>
@@ -7263,8 +7267,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H163" s="1" t="n"/>
-      <c r="I163" s="1" t="n"/>
+      <c r="H163" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I163" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J163" s="1" t="n">
         <v>0</v>
       </c>
@@ -7469,8 +7477,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H168" s="1" t="n"/>
-      <c r="I168" s="1" t="n"/>
+      <c r="H168" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I168" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="J168" s="1" t="n">
         <v>0</v>
       </c>
@@ -7507,8 +7519,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H169" s="1" t="n"/>
-      <c r="I169" s="1" t="n"/>
+      <c r="H169" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I169" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J169" s="1" t="n">
         <v>0</v>
       </c>
@@ -7873,8 +7889,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H178" s="1" t="n"/>
-      <c r="I178" s="1" t="n"/>
+      <c r="H178" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I178" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J178" s="1" t="n">
         <v>0</v>
       </c>
@@ -7911,8 +7931,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H179" s="1" t="n"/>
-      <c r="I179" s="1" t="n"/>
+      <c r="H179" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I179" s="1" t="n">
+        <v>22</v>
+      </c>
       <c r="J179" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -7645,8 +7645,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H172" s="1" t="n"/>
-      <c r="I172" s="1" t="n"/>
+      <c r="H172" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I172" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J172" s="1" t="n">
         <v>0</v>
       </c>
@@ -7683,8 +7687,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H173" s="1" t="n"/>
-      <c r="I173" s="1" t="n"/>
+      <c r="H173" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I173" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J173" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -8233,8 +8233,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H186" s="1" t="n"/>
-      <c r="I186" s="1" t="n"/>
+      <c r="H186" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I186" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J186" s="1" t="n">
         <v>0</v>
       </c>
@@ -8271,8 +8275,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H187" s="1" t="n"/>
-      <c r="I187" s="1" t="n"/>
+      <c r="H187" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I187" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="J187" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -8317,8 +8317,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H188" s="1" t="n"/>
-      <c r="I188" s="1" t="n"/>
+      <c r="H188" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I188" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J188" s="1" t="n">
         <v>0</v>
       </c>
@@ -8355,8 +8359,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H189" s="1" t="n"/>
-      <c r="I189" s="1" t="n"/>
+      <c r="H189" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I189" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J189" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -9161,8 +9161,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H210" s="1" t="n"/>
-      <c r="I210" s="1" t="n"/>
+      <c r="H210" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I210" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J210" s="1" t="n">
         <v>0</v>
       </c>
@@ -9199,8 +9203,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H211" s="1" t="n"/>
-      <c r="I211" s="1" t="n"/>
+      <c r="H211" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I211" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J211" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -8477,8 +8477,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H192" s="1" t="n"/>
-      <c r="I192" s="1" t="n"/>
+      <c r="H192" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I192" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J192" s="1" t="n">
         <v>0</v>
       </c>
@@ -8515,8 +8519,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H193" s="1" t="n"/>
-      <c r="I193" s="1" t="n"/>
+      <c r="H193" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I193" s="1" t="n">
+        <v>29</v>
+      </c>
       <c r="J193" s="1" t="n">
         <v>0</v>
       </c>
@@ -8553,8 +8561,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H194" s="1" t="n"/>
-      <c r="I194" s="1" t="n"/>
+      <c r="H194" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I194" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J194" s="1" t="n">
         <v>0</v>
       </c>
@@ -8591,8 +8603,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H195" s="1" t="n"/>
-      <c r="I195" s="1" t="n"/>
+      <c r="H195" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I195" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J195" s="1" t="n">
         <v>0</v>
       </c>
@@ -8629,8 +8645,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H196" s="1" t="n"/>
-      <c r="I196" s="1" t="n"/>
+      <c r="H196" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I196" s="1" t="n">
+        <v>43</v>
+      </c>
       <c r="J196" s="1" t="n">
         <v>0</v>
       </c>
@@ -8667,8 +8687,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H197" s="1" t="n"/>
-      <c r="I197" s="1" t="n"/>
+      <c r="H197" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="I197" s="1" t="n">
+        <v>13</v>
+      </c>
       <c r="J197" s="1" t="n">
         <v>0</v>
       </c>
@@ -8705,8 +8729,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H198" s="1" t="n"/>
-      <c r="I198" s="1" t="n"/>
+      <c r="H198" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I198" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J198" s="1" t="n">
         <v>0</v>
       </c>
@@ -8743,8 +8771,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H199" s="1" t="n"/>
-      <c r="I199" s="1" t="n"/>
+      <c r="H199" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I199" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="J199" s="1" t="n">
         <v>0</v>
       </c>
@@ -8857,10 +8889,14 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H202" s="1" t="n"/>
-      <c r="I202" s="1" t="n"/>
+      <c r="H202" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I202" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J202" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" ht="15.5" customHeight="1">
@@ -8895,10 +8931,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H203" s="1" t="n"/>
-      <c r="I203" s="1" t="n"/>
+      <c r="H203" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I203" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="J203" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" ht="15.5" customHeight="1">
@@ -8933,8 +8973,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H204" s="1" t="n"/>
-      <c r="I204" s="1" t="n"/>
+      <c r="H204" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I204" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J204" s="1" t="n">
         <v>0</v>
       </c>
@@ -8971,8 +9015,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H205" s="1" t="n"/>
-      <c r="I205" s="1" t="n"/>
+      <c r="H205" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I205" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J205" s="1" t="n">
         <v>0</v>
       </c>
@@ -9085,8 +9133,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H208" s="1" t="n"/>
-      <c r="I208" s="1" t="n"/>
+      <c r="H208" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I208" s="1" t="n">
+        <v>28</v>
+      </c>
       <c r="J208" s="1" t="n">
         <v>0</v>
       </c>
@@ -9123,8 +9175,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H209" s="1" t="n"/>
-      <c r="I209" s="1" t="n"/>
+      <c r="H209" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I209" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="J209" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -8401,8 +8401,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H190" s="1" t="n"/>
-      <c r="I190" s="1" t="n"/>
+      <c r="H190" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I190" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="J190" s="1" t="n">
         <v>0</v>
       </c>
@@ -8439,8 +8443,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H191" s="1" t="n"/>
-      <c r="I191" s="1" t="n"/>
+      <c r="H191" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I191" s="1" t="n">
+        <v>16</v>
+      </c>
       <c r="J191" s="1" t="n">
         <v>0</v>
       </c>
@@ -8813,8 +8821,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H200" s="1" t="n"/>
-      <c r="I200" s="1" t="n"/>
+      <c r="H200" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I200" s="1" t="n">
+        <v>17</v>
+      </c>
       <c r="J200" s="1" t="n">
         <v>0</v>
       </c>
@@ -8851,8 +8863,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H201" s="1" t="n"/>
-      <c r="I201" s="1" t="n"/>
+      <c r="H201" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I201" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J201" s="1" t="n">
         <v>0</v>
       </c>
@@ -9301,8 +9317,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H212" s="1" t="n"/>
-      <c r="I212" s="1" t="n"/>
+      <c r="H212" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I212" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="J212" s="1" t="n">
         <v>0</v>
       </c>
@@ -9339,8 +9359,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H213" s="1" t="n"/>
-      <c r="I213" s="1" t="n"/>
+      <c r="H213" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I213" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="J213" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -9073,8 +9073,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H206" s="1" t="n"/>
-      <c r="I206" s="1" t="n"/>
+      <c r="H206" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I206" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="J206" s="1" t="n">
         <v>0</v>
       </c>
@@ -9111,8 +9115,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H207" s="1" t="n"/>
-      <c r="I207" s="1" t="n"/>
+      <c r="H207" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I207" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="J207" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -9409,8 +9409,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H214" s="1" t="n"/>
-      <c r="I214" s="1" t="n"/>
+      <c r="H214" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I214" s="1" t="n">
+        <v>38</v>
+      </c>
       <c r="J214" s="1" t="n">
         <v>0</v>
       </c>
@@ -9447,8 +9451,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H215" s="1" t="n"/>
-      <c r="I215" s="1" t="n"/>
+      <c r="H215" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="I215" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="J215" s="1" t="n">
         <v>0</v>
       </c>

--- a/DBs/nfl/Results/NFL_2026_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2026_Results.xlsx
@@ -9493,8 +9493,12 @@
           <t>H</t>
         </is>
       </c>
-      <c r="H216" s="1" t="n"/>
-      <c r="I216" s="1" t="n"/>
+      <c r="H216" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I216" s="1" t="n">
+        <v>19</v>
+      </c>
       <c r="J216" s="1" t="n">
         <v>0</v>
       </c>
@@ -9531,8 +9535,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H217" s="1" t="n"/>
-      <c r="I217" s="1" t="n"/>
+      <c r="H217" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I217" s="1" t="n">
+        <v>27</v>
+      </c>
       <c r="J217" s="1" t="n">
         <v>0</v>
       </c>
